--- a/data/trans_orig/IP19C09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51313</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99832</t>
+          <t>99465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71521</t>
+          <t>71355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76881</t>
+          <t>76888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52882</t>
+          <t>52879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83451</t>
+          <t>83214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95021</t>
+          <t>94622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>87828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184592</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191743</t>
+          <t>191782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64024</t>
+          <t>63596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69433</t>
+          <t>69418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119176</t>
+          <t>118832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70027</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75069</t>
+          <t>75067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>315121</t>
+          <t>314106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>321750</t>
+          <t>321229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324088</t>
+          <t>324306</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>334773</t>
+          <t>335165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642025</t>
+          <t>642542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>654682</t>
+          <t>654940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>37434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81124</t>
+          <t>80898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47748</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94018</t>
+          <t>94393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>74925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84927</t>
+          <t>84175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>91486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178367</t>
+          <t>178434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183272</t>
+          <t>183281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76260</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81620</t>
+          <t>81619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69044</t>
+          <t>69844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147048</t>
+          <t>148049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154414</t>
+          <t>154454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>58863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>318994</t>
+          <t>318982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>327004</t>
+          <t>327258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328544</t>
+          <t>328092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>336029</t>
+          <t>336162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>650729</t>
+          <t>650714</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>661956</t>
+          <t>661822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79301</t>
+          <t>79592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88556</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50974</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101131</t>
+          <t>101595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>107094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24220</t>
+          <t>24037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26871</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53952</t>
+          <t>54921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59775</t>
+          <t>59776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98827</t>
+          <t>98477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105138</t>
+          <t>105268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95249</t>
+          <t>94561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197224</t>
+          <t>197120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204675</t>
+          <t>204704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133937</t>
+          <t>134459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>57895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>313387</t>
+          <t>314083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>323855</t>
+          <t>323893</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322713</t>
+          <t>322884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332788</t>
+          <t>332728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640055</t>
+          <t>640822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>654616</t>
+          <t>654513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4363</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2941</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48743</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46868</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54063</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50432</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51047</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48743</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46417</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99465</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1883</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5059</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36397</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34422</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>38615</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35439</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35585</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40437</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36397</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71355</t>
+          <t>71385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76888</t>
+          <t>76902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,92 +1408,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4855</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1791</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51578</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48534</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52876</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51578</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48514</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>52879</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>129</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>83511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87895</t>
+          <t>87897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8517</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3515</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8326</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91581</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87637</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94188</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>97521</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94622</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95012</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91581</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>87828</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94206</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>284</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>184606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191782</t>
+          <t>191746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,92 +2094,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5812</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2108</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,19%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67927</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>64223</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69424</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67927</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>63596</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69418</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118832</t>
+          <t>118989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124080</t>
+          <t>124081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3673</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34373</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31549</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>88,31%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>39267</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>36327</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>34999</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,17%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>90,82%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>34373</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>31105</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>87,06%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>70256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>75070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6656</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18190</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>3964</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8992</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8378</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6523</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17382</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>330598</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>323498</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>335032</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,75%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>319134</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>314106</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>321229</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>314720</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>321254</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>330598</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>324306</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>335165</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,75%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642542</t>
+          <t>642685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>654940</t>
+          <t>654970</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3362,102 +3362,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>764</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3159</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40181</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37180</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44629</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42234</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41117</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>45393</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,32%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40181</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37434</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>122</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80898</t>
+          <t>80047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>45393</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>45393</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>45393</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5846</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4396</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5313</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50913</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46531</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52377</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>46886</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50913</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47981</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>52377</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>141</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94393</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52377</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52377</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52377</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46886</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46886</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46886</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>52377</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>52377</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>52377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,102 +4048,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2956</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5216</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38350</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35525</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39072</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40487</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38113</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>41069</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38350</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36102</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>39072</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>116</t>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74925</t>
+          <t>75248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39072</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39072</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39072</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>41069</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>41069</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>41069</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39072</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39072</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4283</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4007</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94161</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95462</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>87748</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>84175</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>84451</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>88458</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,2%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94161</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91486</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95462</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>261</t>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178434</t>
+          <t>178492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183281</t>
+          <t>183274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>95462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>95462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>88458</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>88458</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>88458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>95462</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>95462</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>95462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2821</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2180</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3018</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72189</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>70041</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72862</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>80048</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76274</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>81619</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76515</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>81626</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72189</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>69844</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>72862</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148049</t>
+          <t>148185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154454</t>
+          <t>154163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72862</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>72862</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>72862</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>72862</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>72862</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>72862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4396</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4384</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>5,5%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4611</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1412</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>24278</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>21294</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>21306</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>94,5%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>58596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9282</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10741</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10840</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4862</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10080</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>333310</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>328890</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>336175</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>324075</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>318982</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>327258</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>318883</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>327082</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>333310</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>328092</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>336162</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>650714</t>
+          <t>650159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>661822</t>
+          <t>661637</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>338172</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>338172</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>338172</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>470</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>329723</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>329723</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>329723</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>338172</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>338172</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>338172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1798</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1923</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6377</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5941</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8936</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -6105,74 +6105,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40892</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39521</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35067</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35503</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>41444</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>45637</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40952</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48061</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,09%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>122</t>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79592</t>
+          <t>79742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88813</t>
+          <t>88506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49888</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49888</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49888</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>41444</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41444</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41444</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49888</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49888</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6340,67 +6340,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1297</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4047</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47773</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53714</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50964</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>51007</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>55011</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47932</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>52742</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101595</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107094</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55011</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>55011</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>55011</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>52742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>52742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>52742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1341</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4157</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6791,74 +6791,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30940</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27231</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27263</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24037</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24447</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>28604</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30940</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28342</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31788</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>84</t>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54921</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31788</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31788</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31788</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28604</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28604</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28604</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>31788</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31788</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2946</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7551</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98719</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95801</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100127</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>103082</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98477</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>105268</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>99406</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>105279</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98719</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>94561</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>100127</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197120</t>
+          <t>197223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204704</t>
+          <t>204660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>100127</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>100127</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>100127</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>106028</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>106028</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>106028</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>100127</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>100127</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>100127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3849</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3562</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72159</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>65356</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62278</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>62565</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>66127</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72159</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>195</t>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134459</t>
+          <t>134465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7595,52 +7595,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>72159</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>72159</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>72159</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>66127</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>66127</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>66127</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>72159</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>72159</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>72159</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,107 +7707,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3751</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3725</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -7820,74 +7820,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29951</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26939</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>30690</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>30929</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>29951</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>27183</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>30690</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57895</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30690</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>30690</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>30690</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>30929</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>30929</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>30929</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>30690</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>30690</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>30690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14010</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>8278</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14060</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14899</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4666</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>328778</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>323384</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>332878</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>319865</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>314083</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>323893</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>313244</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>323799</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,48%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>328778</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>322884</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>332728</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640822</t>
+          <t>640278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>654513</t>
+          <t>654338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>337394</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>337394</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>337394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>328143</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>328143</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>328143</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>337394</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>337394</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>337394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
